--- a/output/pdf_financials_xlsx/MCF.xlsx
+++ b/output/pdf_financials_xlsx/MCF.xlsx
@@ -1255,7 +1255,7 @@
         <v>-0.055049</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.053108</v>
+        <v>-0.053108</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>-0.424029</v>
@@ -1264,7 +1264,7 @@
         <v>-0.860958</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.130046</v>
+        <v>-0.130046</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>1.091735</v>
@@ -1539,7 +1539,7 @@
         <v>-0.055049</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.053108</v>
+        <v>-0.053108</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-0.424029</v>
@@ -1548,7 +1548,7 @@
         <v>-0.853752</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.130046</v>
+        <v>-0.130046</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>0.745277</v>
@@ -1704,7 +1704,7 @@
         <v>-0.055049</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.053108</v>
+        <v>-0.053108</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>-0.424029</v>
@@ -1713,7 +1713,7 @@
         <v>-0.853752</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.130046</v>
+        <v>-0.130046</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>0.745277</v>
@@ -1950,7 +1950,7 @@
         <v>-0.055049</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.053108</v>
+        <v>-0.053108</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.424029</v>
@@ -1959,7 +1959,7 @@
         <v>-0.860958</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.130046</v>
+        <v>-0.130046</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>1.091735</v>
@@ -2060,7 +2060,7 @@
         <v>-0.055049</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.053108</v>
+        <v>-0.053108</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.424029</v>
@@ -2069,7 +2069,7 @@
         <v>-0.860958</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.130046</v>
+        <v>-0.130046</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>1.091735</v>
@@ -2202,7 +2202,7 @@
         <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-0</v>
@@ -2211,7 +2211,7 @@
         <v>-0.8369746259399412</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>31.73462424489459</v>
@@ -5667,7 +5667,7 @@
         <v>0.017749</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.017749</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0</v>
@@ -20636,7 +20636,11 @@
           <t>SHARE-BASED PAYMENT RESERVE (Note 3) -</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -65741,10 +65745,10 @@
         </is>
       </c>
       <c r="L603" s="5" t="n">
-        <v>0.130046</v>
+        <v>-0.130046</v>
       </c>
       <c r="M603" s="5" t="n">
-        <v>0.10005</v>
+        <v>-0.10005</v>
       </c>
       <c r="N603" t="inlineStr">
         <is>
@@ -68496,10 +68500,10 @@
         </is>
       </c>
       <c r="I632" s="5" t="n">
-        <v>0.053108</v>
+        <v>-0.053108</v>
       </c>
       <c r="J632" s="5" t="n">
-        <v>0.424029</v>
+        <v>-0.424029</v>
       </c>
       <c r="K632" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MCF.xlsx
+++ b/output/pdf_financials_xlsx/MCF.xlsx
@@ -1035,16 +1035,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000343</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.007778</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.004622</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001037</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -1065,10 +1065,10 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.462</v>
       </c>
     </row>
     <row r="13">
@@ -1950,16 +1950,16 @@
         <v>-0.055049</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.053108</v>
+        <v>-0.052765</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.424029</v>
+        <v>-0.431807</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.860958</v>
+        <v>-0.86558</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.130046</v>
+        <v>-0.129009</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>1.091735</v>
@@ -1980,10 +1980,10 @@
         <v>-0.132147</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.515</v>
+        <v>-0.511</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-10.808</v>
+        <v>-11.27</v>
       </c>
     </row>
     <row r="28">
@@ -2060,16 +2060,16 @@
         <v>-0.055049</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.053108</v>
+        <v>-0.052765</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.424029</v>
+        <v>-0.431807</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.860958</v>
+        <v>-0.86558</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.130046</v>
+        <v>-0.129009</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>1.091735</v>
@@ -2090,10 +2090,10 @@
         <v>-0.132147</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.515</v>
+        <v>-0.511</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-10.808</v>
+        <v>-11.27</v>
       </c>
     </row>
     <row r="30">
@@ -2339,16 +2339,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.040459</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.032182</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.032182</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.027369</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0.00228</v>
@@ -2363,13 +2363,13 @@
         <v>0.168822</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.251245</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>2.957089</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.252289</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>0.747438</v>
@@ -2378,7 +2378,7 @@
         <v>0.029661</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.000744</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>9.960000000000001</v>
@@ -2449,16 +2449,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.040459</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.032182</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.032182</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.027369</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0.00228</v>
@@ -2473,13 +2473,13 @@
         <v>0.168822</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.251245</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>2.957089</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.252289</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>0.747438</v>
@@ -2488,7 +2488,7 @@
         <v>0.029661</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.000744</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>9.960000000000001</v>
@@ -3109,16 +3109,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.040459</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.032182</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.032182</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.027369</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
@@ -3133,13 +3133,13 @@
         <v>0.003641</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.688303</v>
+        <v>0.437058</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>4.162266</v>
+        <v>1.205177</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.63237</v>
+        <v>1.380081</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0.666338</v>
@@ -3148,7 +3148,7 @@
         <v>0.06125</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.7e-05</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>0.025</v>
@@ -11828,7 +11828,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -14382,7 +14382,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -16586,7 +16586,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -19298,7 +19298,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
@@ -20152,7 +20152,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -47704,7 +47704,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -51064,7 +51064,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
@@ -52886,7 +52886,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
@@ -65512,7 +65512,7 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
@@ -67202,7 +67202,7 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
